--- a/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_circular_pol.xlsx
+++ b/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_circular_pol.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\Poincare beams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A70B61-DE67-4020-AF42-FABC8CF80B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE21BCF8-614E-4743-A2FF-DAFD183E1EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="240" windowWidth="11640" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="525" yWindow="990" windowWidth="12630" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
